--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_27_3.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_27_3.xlsx
@@ -517,52 +517,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999989580264104</v>
+        <v>0.9999996470021449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6671357950315365</v>
+        <v>0.7062024456626972</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999898612771947</v>
+        <v>0.9999981994255731</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9999983256823601</v>
+        <v>0.9999978829121594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9999937704987309</v>
+        <v>0.9999980803930006</v>
       </c>
       <c r="G2" t="n">
-        <v>6.185605337223317e-07</v>
+        <v>2.095547754828813e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1976025710542327</v>
+        <v>0.1744109196481399</v>
       </c>
       <c r="I2" t="n">
-        <v>3.56940687003058e-06</v>
+        <v>5.24254853929329e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>2.110694931863731e-07</v>
+        <v>7.588704041119342e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.890238181608477e-06</v>
+        <v>6.415626290206317e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002230267602403945</v>
+        <v>0.000109200084582549</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0007864861942350492</v>
+        <v>0.000457771531970787</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000000409956822</v>
+        <v>1.000000138884402</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0008199685397745</v>
+        <v>0.0004772598138044906</v>
       </c>
       <c r="P2" t="n">
-        <v>198.5917415561606</v>
+        <v>200.7565613472125</v>
       </c>
       <c r="Q2" t="n">
-        <v>302.1961866699577</v>
+        <v>304.3610064610096</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +572,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999989708541599</v>
+        <v>0.9999996474870492</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6671308747697561</v>
+        <v>0.7062001119948502</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999900405883237</v>
+        <v>0.9999982311623425</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999983608774812</v>
+        <v>0.9999978807895873</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999938818321156</v>
+        <v>0.9999980930788751</v>
       </c>
       <c r="G3" t="n">
-        <v>6.109454274456011e-07</v>
+        <v>2.092669153752715e-07</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1976054919341698</v>
+        <v>0.1744123050141831</v>
       </c>
       <c r="I3" t="n">
-        <v>3.506279157772462e-06</v>
+        <v>5.150143831035225e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>2.066326908876157e-07</v>
+        <v>7.596312403491223e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>1.856455924330039e-06</v>
+        <v>6.373228117263224e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002282125662374589</v>
+        <v>0.0001128786397929664</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0007816299811583491</v>
+        <v>0.0004574570093192054</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000000404909839</v>
+        <v>1.00000013869362</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0008149055876533778</v>
+        <v>0.0004769319012724795</v>
       </c>
       <c r="P3" t="n">
-        <v>198.6165163970936</v>
+        <v>200.7593105854609</v>
       </c>
       <c r="Q3" t="n">
-        <v>302.2209615108906</v>
+        <v>304.3637556992579</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +627,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999989840051199</v>
+        <v>0.9999996482368004</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6671255260953697</v>
+        <v>0.7061966898637002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9999902354074259</v>
+        <v>0.9999982687178387</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9999984000690552</v>
+        <v>0.9999978790525832</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9999940029921952</v>
+        <v>0.9999981084589624</v>
       </c>
       <c r="G4" t="n">
-        <v>6.031384495138751e-07</v>
+        <v>2.088218306490885e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1976086671383362</v>
+        <v>0.174414336539062</v>
       </c>
       <c r="I4" t="n">
-        <v>3.437691757255796e-06</v>
+        <v>5.040797331134578e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.016920837542881e-07</v>
+        <v>7.602538696913113e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.819691920505042e-06</v>
+        <v>6.32182546408077e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002340885732505742</v>
+        <v>0.0001169376678695671</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007766198874055925</v>
+        <v>0.0004569702732663127</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000000399735691</v>
+        <v>1.000000138398636</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0008096822038372425</v>
+        <v>0.0004764244438581326</v>
       </c>
       <c r="P4" t="n">
-        <v>198.6422381307793</v>
+        <v>200.7635688669722</v>
       </c>
       <c r="Q4" t="n">
-        <v>302.2466832445764</v>
+        <v>304.3680139807693</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +682,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.99999899743577</v>
+        <v>0.9999996486693929</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6671197865365073</v>
+        <v>0.7061929181016734</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999904482242424</v>
+        <v>0.9999983102556895</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9999984428289672</v>
+        <v>0.9999978768542145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9999941353343926</v>
+        <v>0.9999981254205219</v>
       </c>
       <c r="G5" t="n">
-        <v>5.951654354441966e-07</v>
+        <v>2.085650250574629e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1976120743884131</v>
+        <v>0.1744165756199328</v>
       </c>
       <c r="I5" t="n">
-        <v>3.362768138031381e-06</v>
+        <v>4.919855816258636e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.963016412636759e-07</v>
+        <v>7.610418752414202e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.779534889647528e-06</v>
+        <v>6.265137284336418e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002404895449711164</v>
+        <v>0.0001213736224222507</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0007714696594450079</v>
+        <v>0.0004566891996286565</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0000003944515</v>
+        <v>1.000000138228436</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0008043127200099342</v>
+        <v>0.0004761314043338188</v>
       </c>
       <c r="P5" t="n">
-        <v>198.6688528545683</v>
+        <v>200.7660299470999</v>
       </c>
       <c r="Q5" t="n">
-        <v>302.2732979683653</v>
+        <v>304.3704750608969</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +737,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999990106725545</v>
+        <v>0.9999996476989601</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6671132505396438</v>
+        <v>0.7061898222963651</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9999906782482513</v>
+        <v>0.9999983531983289</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9999984881783476</v>
+        <v>0.9999978645410711</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9999942781967703</v>
+        <v>0.9999981375227717</v>
       </c>
       <c r="G6" t="n">
-        <v>5.873075083725535e-07</v>
+        <v>2.091411159167631e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1976159544384916</v>
+        <v>0.1744184134236957</v>
       </c>
       <c r="I6" t="n">
-        <v>3.281786608763133e-06</v>
+        <v>4.794824121854994e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.905847626370733e-07</v>
+        <v>7.654555230361311e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.736185685700103e-06</v>
+        <v>6.224689676108152e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002476212789351294</v>
+        <v>0.0001264436198015095</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0007663599078582814</v>
+        <v>0.0004573194899813074</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000000389243585</v>
+        <v>1.000000138610245</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0007989854357195167</v>
+        <v>0.0004767885274516629</v>
       </c>
       <c r="P6" t="n">
-        <v>198.6954345798777</v>
+        <v>200.7605132340994</v>
       </c>
       <c r="Q6" t="n">
-        <v>302.2998796936748</v>
+        <v>304.3649583478965</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +792,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999990238690835</v>
+        <v>0.9999996462735912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6671061836806762</v>
+        <v>0.706186264874</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9999909320797835</v>
+        <v>0.999998401301979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9999985394658302</v>
+        <v>0.9999978511808018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9999944361039312</v>
+        <v>0.9999981513115619</v>
       </c>
       <c r="G7" t="n">
-        <v>5.794734787344384e-07</v>
+        <v>2.099872764722343e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1976201496312471</v>
+        <v>0.1744205252632842</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192423477712446e-06</v>
+        <v>4.6547656400974e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.841193090627471e-07</v>
+        <v>7.70244513289405e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.688271393387596e-06</v>
+        <v>6.178605386495725e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002556932008632444</v>
+        <v>0.0001319179262970032</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0007612315539534855</v>
+        <v>0.0004582436867783716</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000000384051508</v>
+        <v>1.000000139171046</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0007936387571718376</v>
+        <v>0.0004777520692197293</v>
       </c>
       <c r="P7" t="n">
-        <v>198.7222918819741</v>
+        <v>200.7524377925839</v>
       </c>
       <c r="Q7" t="n">
-        <v>302.3267369957712</v>
+        <v>304.3568829063809</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +847,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999990362070804</v>
+        <v>0.99999964443155</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6670983230836403</v>
+        <v>0.7061817722821303</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9999912044218597</v>
+        <v>0.9999984564816042</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9999985943618612</v>
+        <v>0.9999978376883495</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9999946054990669</v>
+        <v>0.9999981680778189</v>
       </c>
       <c r="G8" t="n">
-        <v>5.721491107612318e-07</v>
+        <v>2.110807916853132e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1976248160212078</v>
+        <v>0.1744231922598879</v>
       </c>
       <c r="I8" t="n">
-        <v>3.096543582712172e-06</v>
+        <v>4.494104764725322e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>1.771989510817302e-07</v>
+        <v>7.750808844832305e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.636871266896951e-06</v>
+        <v>6.122569937839256e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002644776606846091</v>
+        <v>0.0001380522857656111</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0007564053878451897</v>
+        <v>0.0004594352965166185</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000000379197214</v>
+        <v>1.000000139895784</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0007886071311807705</v>
+        <v>0.0004789944082515056</v>
       </c>
       <c r="P8" t="n">
-        <v>198.7477323927791</v>
+        <v>200.7420497555499</v>
       </c>
       <c r="Q8" t="n">
-        <v>302.3521775065761</v>
+        <v>304.3464948693469</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +902,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999990472692254</v>
+        <v>0.9999996408802015</v>
       </c>
       <c r="C9" t="n">
-        <v>0.667089431194435</v>
+        <v>0.7061771734077251</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9999915005984968</v>
+        <v>0.9999985125847918</v>
       </c>
       <c r="E9" t="n">
-        <v>0.999998655787403</v>
+        <v>0.9999978166974219</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9999947900775229</v>
+        <v>0.9999981812929671</v>
       </c>
       <c r="G9" t="n">
-        <v>5.655821436362157e-07</v>
+        <v>2.131890255471369e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1976300946307497</v>
+        <v>0.1744259223503959</v>
       </c>
       <c r="I9" t="n">
-        <v>2.992272567176551e-06</v>
+        <v>4.330754847311055e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.694554634279822e-07</v>
+        <v>7.82605085139243e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.580864015302266e-06</v>
+        <v>6.078402849351742e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002742897420502429</v>
+        <v>0.0001449153559354149</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0007520519554101403</v>
+        <v>0.0004617239711636563</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000000374844895</v>
+        <v>1.000000141293035</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0007840683641141136</v>
+        <v>0.0004813805165164774</v>
       </c>
       <c r="P9" t="n">
-        <v>198.7708205870395</v>
+        <v>200.7221732417984</v>
       </c>
       <c r="Q9" t="n">
-        <v>302.3752657008365</v>
+        <v>304.3266183555955</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +957,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999990556023108</v>
+        <v>0.9999996364792795</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6670799935474774</v>
+        <v>0.7061712476921507</v>
       </c>
       <c r="D10" t="n">
-        <v>0.999991814245981</v>
+        <v>0.9999985787100315</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9999987193101669</v>
+        <v>0.9999977938585757</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9999949852268578</v>
+        <v>0.9999981980305076</v>
       </c>
       <c r="G10" t="n">
-        <v>5.606352641543883e-07</v>
+        <v>2.158016029491795e-07</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1976356972256688</v>
+        <v>0.1744294401111385</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88185082011411e-06</v>
+        <v>4.138224744882042e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>1.614475936715179e-07</v>
+        <v>7.907916724697489e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>1.521649206892814e-06</v>
+        <v>6.022463375989732e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002852957831572439</v>
+        <v>0.0001524914455310725</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0007487558107650238</v>
+        <v>0.000464544511267951</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000000371566304</v>
+        <v>1.000000143024546</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0007806318957674945</v>
+        <v>0.0004843211328523349</v>
       </c>
       <c r="P10" t="n">
-        <v>198.7883905917747</v>
+        <v>200.6978127124225</v>
       </c>
       <c r="Q10" t="n">
-        <v>302.3928357055717</v>
+        <v>304.3022578262195</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1012,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999990607514819</v>
+        <v>0.9999996292561524</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6670697622753546</v>
+        <v>0.7061655081826561</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9999921504947277</v>
+        <v>0.9999986468307559</v>
       </c>
       <c r="E11" t="n">
-        <v>0.999998786003702</v>
+        <v>0.9999977589295973</v>
       </c>
       <c r="F11" t="n">
-        <v>0.999995194146346</v>
+        <v>0.9999982089785026</v>
       </c>
       <c r="G11" t="n">
-        <v>5.575784937587162e-07</v>
+        <v>2.200895632303824e-07</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1976417709507688</v>
+        <v>0.1744328473319084</v>
       </c>
       <c r="I11" t="n">
-        <v>2.763472143721128e-06</v>
+        <v>3.93988459347416e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>1.530400070133832e-07</v>
+        <v>8.033119691837683e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>1.458256075367255e-06</v>
+        <v>5.985873467573815e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000297496266522443</v>
+        <v>0.0001609740812291169</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0007467117876120051</v>
+        <v>0.0004691370409916301</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000000369540401</v>
+        <v>1.000000145866432</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0007785008543171405</v>
+        <v>0.0004891091760741981</v>
       </c>
       <c r="P11" t="n">
-        <v>198.7993250950864</v>
+        <v>200.6584625356928</v>
       </c>
       <c r="Q11" t="n">
-        <v>302.4037702088834</v>
+        <v>304.2629076494899</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1067,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999990610460305</v>
+        <v>0.99999961953637</v>
       </c>
       <c r="C12" t="n">
-        <v>0.667058476048508</v>
+        <v>0.7061591349039034</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999925062557771</v>
+        <v>0.9999987215027977</v>
       </c>
       <c r="E12" t="n">
-        <v>0.999998858989149</v>
+        <v>0.9999977144373291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9999954156923602</v>
+        <v>0.9999982174573122</v>
       </c>
       <c r="G12" t="n">
-        <v>5.574036369478877e-07</v>
+        <v>2.258596459742079e-07</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1976484709425646</v>
+        <v>0.1744366307854873</v>
       </c>
       <c r="I12" t="n">
-        <v>2.638224027345168e-06</v>
+        <v>3.722469640967011e-07</v>
       </c>
       <c r="J12" t="n">
-        <v>1.438392431146104e-07</v>
+        <v>8.192602283179508e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>1.391031635229889e-06</v>
+        <v>5.957535962073259e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0003111083030152879</v>
+        <v>0.0001703638232772787</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0007465946938921329</v>
+        <v>0.0004752469315778987</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000000369424513</v>
+        <v>1.000000149690609</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000778378775675196</v>
+        <v>0.0004954791773519411</v>
       </c>
       <c r="P12" t="n">
-        <v>198.7999523941523</v>
+        <v>200.6067041322178</v>
       </c>
       <c r="Q12" t="n">
-        <v>302.4043975079493</v>
+        <v>304.2111492460149</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1122,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999990552502335</v>
+        <v>0.9999996069839675</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6670460111655376</v>
+        <v>0.7061510945996495</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999928843198466</v>
+        <v>0.9999988074960779</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9999989378281112</v>
+        <v>0.9999976580846287</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999956513927909</v>
+        <v>0.9999982246953821</v>
       </c>
       <c r="G13" t="n">
-        <v>5.608442724599347e-07</v>
+        <v>2.333112942888511e-07</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1976558706355507</v>
+        <v>0.1744414038574154</v>
       </c>
       <c r="I13" t="n">
-        <v>2.505123979846368e-06</v>
+        <v>3.472091795245592e-07</v>
       </c>
       <c r="J13" t="n">
-        <v>1.339005675563937e-07</v>
+        <v>8.394598609276481e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>1.319512273701381e-06</v>
+        <v>5.933345202261036e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000326243838001604</v>
+        <v>0.0001807173092795981</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0007488953681656301</v>
+        <v>0.0004830230784226061</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000000371704826</v>
+        <v>1.000000154629259</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0007807773944155683</v>
+        <v>0.0005035863708666709</v>
       </c>
       <c r="P13" t="n">
-        <v>198.7876451183134</v>
+        <v>200.5417844961597</v>
       </c>
       <c r="Q13" t="n">
-        <v>302.3920902321105</v>
+        <v>304.1462296099568</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999990401960108</v>
+        <v>0.9999995901924629</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6670324387157651</v>
+        <v>0.7061419876698778</v>
       </c>
       <c r="D14" t="n">
-        <v>0.999993272441881</v>
+        <v>0.9999988959146719</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9999990187408876</v>
+        <v>0.9999975903460093</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9999958933588597</v>
+        <v>0.9999982268841214</v>
       </c>
       <c r="G14" t="n">
-        <v>5.697811093430266e-07</v>
+        <v>2.432794568035108e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>0.197663927828035</v>
+        <v>0.1744468101243268</v>
       </c>
       <c r="I14" t="n">
-        <v>2.368482956838285e-06</v>
+        <v>3.214652411672327e-07</v>
       </c>
       <c r="J14" t="n">
-        <v>1.237004607828497e-07</v>
+        <v>8.637407776113539e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>1.246091708810567e-06</v>
+        <v>5.926030093892932e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0003430771077720574</v>
+        <v>0.0001922104644444106</v>
       </c>
       <c r="M14" t="n">
-        <v>0.000754838465728282</v>
+        <v>0.0004932336736309787</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000000377627799</v>
+        <v>1.000000161235752</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0007869735019453701</v>
+        <v>0.0005142316522519099</v>
       </c>
       <c r="P14" t="n">
-        <v>198.7560271371366</v>
+        <v>200.458110052767</v>
       </c>
       <c r="Q14" t="n">
-        <v>302.3604722509337</v>
+        <v>304.0625551665641</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999999013898878</v>
+        <v>0.9999995677260476</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6670177662932011</v>
+        <v>0.7061326691699734</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9999936786525939</v>
+        <v>0.9999989918931187</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9999991036999618</v>
+        <v>0.9999974982999855</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9999961466591025</v>
+        <v>0.9999982193308455</v>
       </c>
       <c r="G15" t="n">
-        <v>5.853922233809262e-07</v>
+        <v>2.56616491427501e-07</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1976726380118847</v>
+        <v>0.1744523419884083</v>
       </c>
       <c r="I15" t="n">
-        <v>2.225473690549076e-06</v>
+        <v>2.93520177727908e-07</v>
       </c>
       <c r="J15" t="n">
-        <v>1.129902655856804e-07</v>
+        <v>8.967346864693889e-07</v>
       </c>
       <c r="K15" t="n">
-        <v>1.169231978067378e-06</v>
+        <v>5.951274320986485e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0003618165926653877</v>
+        <v>0.0002049839532401626</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0007651092885208793</v>
+        <v>0.0005065732833731967</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000000387974212</v>
+        <v>1.000000170074998</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0007976815749277825</v>
+        <v>0.000528139156797653</v>
       </c>
       <c r="P15" t="n">
-        <v>198.7019674941191</v>
+        <v>200.3513662356437</v>
       </c>
       <c r="Q15" t="n">
-        <v>302.3064126079161</v>
+        <v>303.9558113494408</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999989718735484</v>
+        <v>0.9999995365188412</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6670018500485937</v>
+        <v>0.7061252229586541</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9999940811947678</v>
+        <v>0.9999990862939172</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9999991900405021</v>
+        <v>0.9999973702065995</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9999963981181127</v>
+        <v>0.9999981917597598</v>
       </c>
       <c r="G16" t="n">
-        <v>6.103402744202695e-07</v>
+        <v>2.751424372284845e-07</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1976820865822295</v>
+        <v>0.1744567623811071</v>
       </c>
       <c r="I16" t="n">
-        <v>2.083755958592972e-06</v>
+        <v>2.660344619927622e-07</v>
       </c>
       <c r="J16" t="n">
-        <v>1.021059186423875e-07</v>
+        <v>9.426497768547355e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>1.09293093861768e-06</v>
+        <v>6.043421194237489e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0003826689510109937</v>
+        <v>0.0002194047714290174</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0007812427755955696</v>
+        <v>0.0005245402150726716</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000000404508768</v>
+        <v>1.000000182353243</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0008145018979481646</v>
+        <v>0.0005468709779762504</v>
       </c>
       <c r="P16" t="n">
-        <v>198.6184984167764</v>
+        <v>200.2119538396267</v>
       </c>
       <c r="Q16" t="n">
-        <v>302.2229435305734</v>
+        <v>303.8163989534238</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999989106928745</v>
+        <v>0.9999994968201006</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6669848799836489</v>
+        <v>0.706116809656237</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9999944933967192</v>
+        <v>0.9999991860877855</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9999992781057226</v>
+        <v>0.9999972117149669</v>
       </c>
       <c r="F17" t="n">
-        <v>0.999996655539239</v>
+        <v>0.9999981504810309</v>
       </c>
       <c r="G17" t="n">
-        <v>6.46659765321368e-07</v>
+        <v>2.987093245042846e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1976921607458494</v>
+        <v>0.1744617568808575</v>
       </c>
       <c r="I17" t="n">
-        <v>1.938637435724072e-06</v>
+        <v>2.369785012904386e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>9.100415334707895e-08</v>
+        <v>9.994611226192094e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>1.014820794535575e-06</v>
+        <v>6.181381150641159e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0004060773749605915</v>
+        <v>0.000235307759247056</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0008041515810600437</v>
+        <v>0.0005465430673828775</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000000428579853</v>
+        <v>1.000000197972419</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0008383859786890263</v>
+        <v>0.0005698105372614852</v>
       </c>
       <c r="P17" t="n">
-        <v>198.5028910915951</v>
+        <v>200.0475897905143</v>
       </c>
       <c r="Q17" t="n">
-        <v>302.1073362053921</v>
+        <v>303.6520349043114</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9999988245334916</v>
+        <v>0.9999994454467463</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6669661796898987</v>
+        <v>0.7061082306756555</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9999948924669755</v>
+        <v>0.9999992906019209</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9999993661953871</v>
+        <v>0.9999970088235866</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9999969053474538</v>
+        <v>0.999998086959878</v>
       </c>
       <c r="G18" t="n">
-        <v>6.978076968562032e-07</v>
+        <v>3.292067668017432e-07</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1977032620480302</v>
+        <v>0.1744668497343234</v>
       </c>
       <c r="I18" t="n">
-        <v>1.798142016181761e-06</v>
+        <v>2.065481885877644e-07</v>
       </c>
       <c r="J18" t="n">
-        <v>7.989930657794009e-08</v>
+        <v>1.072187563571531e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>9.390206613798506e-07</v>
+        <v>6.393678760796477e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0004330093942175707</v>
+        <v>0.0002530896161119318</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0008353488474022115</v>
+        <v>0.0005737654283779594</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000000462478626</v>
+        <v>1.000000218184887</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0008709113772466244</v>
+        <v>0.0005981918105221835</v>
       </c>
       <c r="P18" t="n">
-        <v>198.3506445561589</v>
+        <v>199.8531596261278</v>
       </c>
       <c r="Q18" t="n">
-        <v>301.955089669956</v>
+        <v>303.4576047399249</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999987067186024</v>
+        <v>0.9999993812546358</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6669468870381452</v>
+        <v>0.7060972866568151</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9999952728389208</v>
+        <v>0.9999994012872915</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9999994489896518</v>
+        <v>0.9999967661742064</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9999971432083603</v>
+        <v>0.9999980050508187</v>
       </c>
       <c r="G19" t="n">
-        <v>7.677477044786067e-07</v>
+        <v>3.673139765786165e-07</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1977147149995102</v>
+        <v>0.174473346576664</v>
       </c>
       <c r="I19" t="n">
-        <v>1.664229465202629e-06</v>
+        <v>1.74321060479449e-07</v>
       </c>
       <c r="J19" t="n">
-        <v>6.946201376763328e-08</v>
+        <v>1.159165264540129e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>8.66845739485131e-07</v>
+        <v>6.667431625097891e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0004677639978293168</v>
+        <v>0.0002727858226868648</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0008762121344050234</v>
+        <v>0.000606064333696198</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000508832025</v>
+        <v>1.000000243440799</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0009135142989758114</v>
+        <v>0.0006318657471077708</v>
       </c>
       <c r="P19" t="n">
-        <v>198.1596093351268</v>
+        <v>199.6340976652592</v>
       </c>
       <c r="Q19" t="n">
-        <v>301.7640544489238</v>
+        <v>303.2385427790563</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999985485192437</v>
+        <v>0.9999992995017971</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6669255079881831</v>
+        <v>0.7060854921741099</v>
       </c>
       <c r="D20" t="n">
-        <v>0.999995616612271</v>
+        <v>0.9999995147410762</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9999995243459302</v>
+        <v>0.9999964575541238</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9999973582925303</v>
+        <v>0.9999978888613502</v>
       </c>
       <c r="G20" t="n">
-        <v>8.616616776427856e-07</v>
+        <v>4.158459931902913e-07</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1977274065270946</v>
+        <v>0.174480348291093</v>
       </c>
       <c r="I20" t="n">
-        <v>1.543201700483248e-06</v>
+        <v>1.412878814893013e-07</v>
       </c>
       <c r="J20" t="n">
-        <v>5.99623757533006e-08</v>
+        <v>1.269790172170088e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>8.015820381182743e-07</v>
+        <v>7.055754969012987e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0005082673112456175</v>
+        <v>0.0002945791671192511</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0009282573337403726</v>
+        <v>0.0006448612201011093</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000000571074396</v>
+        <v>1.00000027560585</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0009677751701952815</v>
+        <v>0.0006723142972875656</v>
       </c>
       <c r="P20" t="n">
-        <v>197.9288062573169</v>
+        <v>199.385901707813</v>
       </c>
       <c r="Q20" t="n">
-        <v>301.5332513711139</v>
+        <v>302.99034682161</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9999983394382513</v>
+        <v>0.9999991932553185</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6669035548587254</v>
+        <v>0.7060774170197206</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999959051717683</v>
+        <v>0.9999996195256859</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9999995881695882</v>
+        <v>0.9999960532555491</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9999975389502688</v>
+        <v>0.9999977178057997</v>
       </c>
       <c r="G21" t="n">
-        <v>9.857811865660023e-07</v>
+        <v>4.789184924963737e-07</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1977404388530665</v>
+        <v>0.174485142051567</v>
       </c>
       <c r="I21" t="n">
-        <v>1.441612351225774e-06</v>
+        <v>1.107788175701559e-07</v>
       </c>
       <c r="J21" t="n">
-        <v>5.191657437734377e-08</v>
+        <v>1.414711047387794e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>7.467644628015592e-07</v>
+        <v>7.627449324789752e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0005532532417863963</v>
+        <v>0.0003191610584816648</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0009928651401706087</v>
+        <v>0.0006920393720709638</v>
       </c>
       <c r="N21" t="n">
-        <v>1.00000065333577</v>
+        <v>1.000000317407744</v>
       </c>
       <c r="O21" t="n">
-        <v>0.001035133464701849</v>
+        <v>0.0007215009208590147</v>
       </c>
       <c r="P21" t="n">
-        <v>197.6596628545804</v>
+        <v>199.1034708316353</v>
       </c>
       <c r="Q21" t="n">
-        <v>301.2641079683775</v>
+        <v>302.7079159454323</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999980662825279</v>
+        <v>0.9999990603819855</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6668799704684387</v>
+        <v>0.7060686731342553</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999961124427906</v>
+        <v>0.9999997202719737</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9999996376956221</v>
+        <v>0.9999955560874869</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9999976694807382</v>
+        <v>0.9999974954079417</v>
       </c>
       <c r="G22" t="n">
-        <v>1.147938223733193e-06</v>
+        <v>5.577978427912206e-07</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1977544395659332</v>
+        <v>0.1744903327996954</v>
       </c>
       <c r="I22" t="n">
-        <v>1.368641166844803e-06</v>
+        <v>8.144555057114522e-08</v>
       </c>
       <c r="J22" t="n">
-        <v>4.567317432475615e-08</v>
+        <v>1.592921002137927e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>7.071571705847794e-07</v>
+        <v>8.370737688211502e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0006033263222217655</v>
+        <v>0.0003462436431733866</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001071418790078461</v>
+        <v>0.0007468586498067894</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000000760806874</v>
+        <v>1.000000369685776</v>
       </c>
       <c r="O22" t="n">
-        <v>0.001117031306114751</v>
+        <v>0.0007786539687396035</v>
       </c>
       <c r="P22" t="n">
-        <v>197.3550861471878</v>
+        <v>198.7985384582244</v>
       </c>
       <c r="Q22" t="n">
-        <v>300.9595312609849</v>
+        <v>302.4029835720215</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.999997712020096</v>
+        <v>0.9999988934855775</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6668545566770923</v>
+        <v>0.7060598423517992</v>
       </c>
       <c r="D23" t="n">
-        <v>0.999996197741149</v>
+        <v>0.9999998114456472</v>
       </c>
       <c r="E23" t="n">
-        <v>0.999999662623169</v>
+        <v>0.9999949401017588</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9999977241423592</v>
+        <v>0.9999972043196981</v>
       </c>
       <c r="G23" t="n">
-        <v>1.358243706575608e-06</v>
+        <v>6.568747601315516e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1977695262902952</v>
+        <v>0.1744955751336312</v>
       </c>
       <c r="I23" t="n">
-        <v>1.338611295009619e-06</v>
+        <v>5.489944386270065e-08</v>
       </c>
       <c r="J23" t="n">
-        <v>4.253073314891464e-08</v>
+        <v>1.813721164251676e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>6.905710140792668e-07</v>
+        <v>9.34360004434532e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0006588966972295254</v>
+        <v>0.0003762998609455352</v>
       </c>
       <c r="M23" t="n">
-        <v>0.001165437131112446</v>
+        <v>0.000810478105892782</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000000900188815</v>
+        <v>1.000000435349937</v>
       </c>
       <c r="O23" t="n">
-        <v>0.001215052202571349</v>
+        <v>0.0008449818367816061</v>
       </c>
       <c r="P23" t="n">
-        <v>197.0186361700113</v>
+        <v>198.4715449209626</v>
       </c>
       <c r="Q23" t="n">
-        <v>300.6230812838083</v>
+        <v>302.0759900347597</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999972588415057</v>
+        <v>0.9999986840943554</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6668284165985868</v>
+        <v>0.7060515813175362</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999961498895309</v>
+        <v>0.9999998879376536</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9999996543588602</v>
+        <v>0.9999941759174161</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999976946658429</v>
+        <v>0.9999968279890177</v>
       </c>
       <c r="G24" t="n">
-        <v>1.627270094121635e-06</v>
+        <v>7.811784347668749e-07</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1977850441700885</v>
+        <v>0.1745004792404279</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3554577852505e-06</v>
+        <v>3.26280481163153e-08</v>
       </c>
       <c r="J24" t="n">
-        <v>4.357255665063759e-08</v>
+        <v>2.087643138481383e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>6.995151709505689e-07</v>
+        <v>1.060135593298849e-06</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0007233236483327411</v>
+        <v>0.0004115178063127184</v>
       </c>
       <c r="M24" t="n">
-        <v>0.001275644971816859</v>
+        <v>0.0008838429921467245</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000001078488588</v>
+        <v>1.000000517733368</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00132995181921623</v>
+        <v>0.0009214700181296299</v>
       </c>
       <c r="P24" t="n">
-        <v>196.6572134721096</v>
+        <v>198.1249244871801</v>
       </c>
       <c r="Q24" t="n">
-        <v>300.2616585859066</v>
+        <v>301.7293696009772</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999966811623454</v>
+        <v>0.9999984234618817</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6668011703546846</v>
+        <v>0.7060415381095079</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9999959083210163</v>
+        <v>0.9999999446945237</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9999996008842085</v>
+        <v>0.9999932424708996</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999975434183963</v>
+        <v>0.9999963523280381</v>
       </c>
       <c r="G25" t="n">
-        <v>1.970205398099612e-06</v>
+        <v>9.359011298782629e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1978012187174454</v>
+        <v>0.1745064413225575</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4405036369039e-06</v>
+        <v>1.610273031072385e-08</v>
       </c>
       <c r="J25" t="n">
-        <v>5.031373129146217e-08</v>
+        <v>2.422237160371424e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>7.454086840976812e-07</v>
+        <v>1.219108918912523e-06</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0007980498346987484</v>
+        <v>0.0004517396404320909</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00140364005289804</v>
+        <v>0.0009674198312409472</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000001305772192</v>
+        <v>1.000000620277292</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001463395915885381</v>
+        <v>0.001008604896292001</v>
       </c>
       <c r="P25" t="n">
-        <v>196.2747455153093</v>
+        <v>197.7635119930401</v>
       </c>
       <c r="Q25" t="n">
-        <v>299.8791906291063</v>
+        <v>301.3679571068371</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999959491911027</v>
+        <v>0.999998096765446</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6667734012077913</v>
+        <v>0.7060335696289767</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999954265230057</v>
+        <v>0.9999999666030756</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9999994876319425</v>
+        <v>0.999992081099639</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999972403909979</v>
+        <v>0.9999957388964336</v>
       </c>
       <c r="G26" t="n">
-        <v>2.404735147257026e-06</v>
+        <v>1.129842246700344e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>0.197817703682606</v>
+        <v>0.1745111717568212</v>
       </c>
       <c r="I26" t="n">
-        <v>1.61012392949644e-06</v>
+        <v>9.723841158257257e-09</v>
       </c>
       <c r="J26" t="n">
-        <v>6.459065093443645e-08</v>
+        <v>2.838530835521249e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>8.373572902154382e-07</v>
+        <v>1.424127338339753e-06</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0008893085341624444</v>
+        <v>0.0004966947196052258</v>
       </c>
       <c r="M26" t="n">
-        <v>0.001550720847624429</v>
+        <v>0.001062940377773064</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000001593760878</v>
+        <v>1.000000748813595</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00161673824454249</v>
+        <v>0.001108191950244781</v>
       </c>
       <c r="P26" t="n">
-        <v>195.876141572703</v>
+        <v>197.3868650793513</v>
       </c>
       <c r="Q26" t="n">
-        <v>299.4805866865001</v>
+        <v>300.9913101931483</v>
       </c>
     </row>
   </sheetData>
